--- a/outputs/design_sweep/design_study/recommended_verified/params.xlsx
+++ b/outputs/design_sweep/design_study/recommended_verified/params.xlsx
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>326.4825</v>
+        <v>337.4825</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>943.1094532973556</v>
+        <v>912.2732232376414</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>471.5547266486778</v>
+        <v>456.1366116188207</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1003.194117647059</v>
+        <v>994.6305988316049</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1050</v>
+        <v>1041.436481184546</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10.00000000000001</v>
+        <v>9.750000000000005</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7.500000000000004</v>
+        <v>7.312500000000004</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>551.1383292383292</v>
+        <v>300</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1019.783333333334</v>
+        <v>991.8608912081182</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1050</v>
+        <v>1022.077557874785</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>9.750000000000005</v>
+        <v>7.250000000000003</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7.312500000000004</v>
+        <v>5.437500000000003</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>130.6</v>
+        <v>144.2267672041623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>709.4</v>
+        <v>723.0267672041624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>337.336</v>
+        <v>380</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>159.069</v>
+        <v>150.8290738714257</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>519.2860000000001</v>
+        <v>538.048711295145</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
